--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>104500</t>
   </si>
   <si>
-    <t>13728.7</t>
+    <t>13726.66</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C616"/>
+  <dimension ref="A1:C617"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7159,10 +7159,21 @@
       <c r="A616" s="2">
         <v>46266</v>
       </c>
-      <c r="B616" t="s">
+      <c r="B616">
+        <v>104500</v>
+      </c>
+      <c r="C616">
+        <v>13728.7</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3">
+      <c r="A617" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B617" t="s">
         <v>3</v>
       </c>
-      <c r="C616" t="s">
+      <c r="C617" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>104500</t>
   </si>
   <si>
-    <t>13726.66</t>
+    <t>13729.92</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C617"/>
+  <dimension ref="A1:C618"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7170,10 +7170,21 @@
       <c r="A617" s="2">
         <v>46267</v>
       </c>
-      <c r="B617" t="s">
+      <c r="B617">
+        <v>104500</v>
+      </c>
+      <c r="C617">
+        <v>13726.66</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3">
+      <c r="A618" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B618" t="s">
         <v>3</v>
       </c>
-      <c r="C617" t="s">
+      <c r="C618" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>104500</t>
   </si>
   <si>
-    <t>13729.92</t>
+    <t>13728.7</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C618"/>
+  <dimension ref="A1:C619"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7181,10 +7181,21 @@
       <c r="A618" s="2">
         <v>46268</v>
       </c>
-      <c r="B618" t="s">
+      <c r="B618">
+        <v>104500</v>
+      </c>
+      <c r="C618">
+        <v>13729.92</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3">
+      <c r="A619" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B619" t="s">
         <v>3</v>
       </c>
-      <c r="C618" t="s">
+      <c r="C619" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -25,10 +25,10 @@
     <t>Avg With Rate(USD/mt,VAT included)</t>
   </si>
   <si>
-    <t>104500</t>
+    <t>105500</t>
   </si>
   <si>
-    <t>13728.7</t>
+    <t>13876.14</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C619"/>
+  <dimension ref="A1:C620"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7192,10 +7192,21 @@
       <c r="A619" s="2">
         <v>46269</v>
       </c>
-      <c r="B619" t="s">
+      <c r="B619">
+        <v>104500</v>
+      </c>
+      <c r="C619">
+        <v>13728.7</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3">
+      <c r="A620" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B620" t="s">
         <v>3</v>
       </c>
-      <c r="C619" t="s">
+      <c r="C620" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>105500</t>
   </si>
   <si>
-    <t>13876.14</t>
+    <t>13878.2</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C620"/>
+  <dimension ref="A1:C621"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7203,10 +7203,21 @@
       <c r="A620" s="2">
         <v>46272</v>
       </c>
-      <c r="B620" t="s">
+      <c r="B620">
+        <v>105500</v>
+      </c>
+      <c r="C620">
+        <v>13876.14</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3">
+      <c r="A621" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B621" t="s">
         <v>3</v>
       </c>
-      <c r="C620" t="s">
+      <c r="C621" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -25,10 +25,10 @@
     <t>Avg With Rate(USD/mt,VAT included)</t>
   </si>
   <si>
-    <t>105500</t>
+    <t>106500</t>
   </si>
   <si>
-    <t>13878.2</t>
+    <t>14011.62</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C621"/>
+  <dimension ref="A1:C622"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7214,10 +7214,21 @@
       <c r="A621" s="2">
         <v>46273</v>
       </c>
-      <c r="B621" t="s">
+      <c r="B621">
+        <v>105500</v>
+      </c>
+      <c r="C621">
+        <v>13878.2</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3">
+      <c r="A622" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B622" t="s">
         <v>3</v>
       </c>
-      <c r="C621" t="s">
+      <c r="C622" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>106500</t>
   </si>
   <si>
-    <t>14011.62</t>
+    <t>14015.79</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C622"/>
+  <dimension ref="A1:C623"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7225,10 +7225,21 @@
       <c r="A622" s="2">
         <v>46274</v>
       </c>
-      <c r="B622" t="s">
+      <c r="B622">
+        <v>106500</v>
+      </c>
+      <c r="C622">
+        <v>14011.62</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3">
+      <c r="A623" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B623" t="s">
         <v>3</v>
       </c>
-      <c r="C622" t="s">
+      <c r="C623" t="s">
         <v>4</v>
       </c>
     </row>

--- a/LME/parser/antimony/data/antimony.xlsx
+++ b/LME/parser/antimony/data/antimony.xlsx
@@ -28,7 +28,7 @@
     <t>106500</t>
   </si>
   <si>
-    <t>14015.79</t>
+    <t>14005.79</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C623"/>
+  <dimension ref="A1:C624"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7236,10 +7236,21 @@
       <c r="A623" s="2">
         <v>46275</v>
       </c>
-      <c r="B623" t="s">
+      <c r="B623">
+        <v>106500</v>
+      </c>
+      <c r="C623">
+        <v>14015.79</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3">
+      <c r="A624" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B624" t="s">
         <v>3</v>
       </c>
-      <c r="C623" t="s">
+      <c r="C624" t="s">
         <v>4</v>
       </c>
     </row>
